--- a/AAII_Financials/Quarterly/BLMN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BLMN_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="92">
   <si>
     <t>BLMN</t>
   </si>
@@ -656,415 +656,427 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45193</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45102</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45011</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44920</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44829</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44738</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44647</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44556</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44465</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44374</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44283</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44192</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44101</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44010</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43919</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43828</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43737</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43464</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43282</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43191</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43002</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42911</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42820</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42729</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42638</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1194200</v>
+      </c>
+      <c r="E8" s="3">
         <v>1079800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1152700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1244700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1095000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1055800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1125200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1140500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1047100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1010500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1077400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>987500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>812500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>771300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>578500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1008300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1022200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>967100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1021900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1128100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1013100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>965000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1031800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1116500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1076400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>955600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1036500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1154700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1004100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1005400</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>352300</v>
+      </c>
+      <c r="E9" s="3">
         <v>321900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>351200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>384200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>326900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>332900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>364500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>359400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>321400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>304300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>311800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>291600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>247700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>230800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>179300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>313200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>312300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>300100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>312400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>351800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>313200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>307500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>322800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>352100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>332600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>296600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>323100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>364700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>310700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>322100</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>841900</v>
+      </c>
+      <c r="E10" s="3">
         <v>757900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>801500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>860500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>768100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>722900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>760700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>781100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>725700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>706200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>765600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>695900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>564800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>540500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>399200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>695100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>709900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>667000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>709500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>776300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>699900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>657500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>709000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>764400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>743800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>659000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>713400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>790000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>693400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>683300</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1097,8 +1109,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1189,8 +1202,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1281,192 +1297,201 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>34400</v>
       </c>
       <c r="E14" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="F14" s="3">
         <v>1800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>107800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>4800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>63500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>7300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>16500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>42600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>71800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>2200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>2000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>2100</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
         <v>0</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-      <c r="Z14" s="3" t="s">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>800</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>300</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
         <v>0</v>
       </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>49300</v>
+      </c>
+      <c r="E15" s="3">
         <v>48000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>47600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>46300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>44400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>42200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>41300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>41800</v>
-      </c>
-      <c r="K15" s="3">
-        <v>40800</v>
       </c>
       <c r="L15" s="3">
         <v>40800</v>
       </c>
       <c r="M15" s="3">
+        <v>40800</v>
+      </c>
+      <c r="N15" s="3">
         <v>40500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>41200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>42800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>43400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>45800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>48300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>49600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>47900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>49800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>49500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>50100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>50600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>50800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>50100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>49800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>47800</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>48100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>46600</v>
-      </c>
-      <c r="AE15" s="3">
-        <v>48600</v>
       </c>
       <c r="AF15" s="3">
         <v>48600</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>48600</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1496,192 +1521,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1137300</v>
+      </c>
+      <c r="E17" s="3">
         <v>1021600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1063200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1124100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1010900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1004500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1145100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1033300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>968600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>995600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>954800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>896500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>819700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>785500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>690600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1049900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>979000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>945200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>978500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1045600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>991700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>952500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>998900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1038100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1061900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>950400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>995400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1077900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1008300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>974100</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>56900</v>
+      </c>
+      <c r="E18" s="3">
         <v>58200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>89500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>120600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>84100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>51300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-19900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>107200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>78500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>14900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>122600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>91000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-7200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-14200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-112100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-41600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>43200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>21900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>43400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>82500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>21400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>12500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>32900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>78400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>14500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>5200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>41100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>76800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-4200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>31300</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1714,8 +1746,9 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1735,11 +1768,11 @@
         <v>0</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>-17700</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
@@ -1753,32 +1786,32 @@
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>300</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-800</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>-100</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
@@ -1789,25 +1822,28 @@
         <v>0</v>
       </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>7500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>7200</v>
       </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
       <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1815,367 +1851,379 @@
         <v>106200</v>
       </c>
       <c r="E21" s="3">
+        <v>106200</v>
+      </c>
+      <c r="F21" s="3">
         <v>137000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>166900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>128500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>93500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>149000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>119300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>55700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>163100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>132200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>35900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>29200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-65800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>5900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>92800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>69900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>93300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>131800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>71500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>63100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>83700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>128500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>64400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>60600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>96400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>123400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>44000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>81900</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E22" s="3">
         <v>12800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>13000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>12400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>14300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>12700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>12500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>13600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>13800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>14200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>15000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>14600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>17800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>18300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>16600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>11700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>12400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>13300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>12400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>11200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>11700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>11600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>11300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>10300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>12000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>10700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>9500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>9100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>12300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>42900</v>
+      </c>
+      <c r="E23" s="3">
         <v>45400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>76500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>108200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>69800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>38600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-50100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>93600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>64700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>107600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>76400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-24700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-32600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-128200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-54100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>30800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>8700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>31000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>71100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>9700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>21600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>68100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>38800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>67600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-16900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>23200</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E24" s="3">
         <v>-100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>6500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>14800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>9700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>5600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>11500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>15900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-4500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>22700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>6600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-10500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-14800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-35800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-19700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>5500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-2700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-12100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-3200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>3000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>18000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-14200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2266,192 +2314,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>45600</v>
+      </c>
+      <c r="E26" s="3">
         <v>45400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>70000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>93400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>60100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>33100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-61700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>77700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>63200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>84900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>69800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-14200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-17800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-92400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-34400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>29300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>9400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>29800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>65600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>12400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>4300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>26700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>66100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>14700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>5300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>35800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>49600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-2700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>21200</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>43300</v>
+      </c>
+      <c r="E27" s="3">
         <v>44500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>68300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>91300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>58000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>32000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-63600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>75500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>60700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>82500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>68900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-14200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-17600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-92300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-38100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>28000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>9200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>29000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>64300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>10900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>4100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>26700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>65400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>13900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>5600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>35100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>48600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-4300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>20700</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2542,8 +2599,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2598,8 +2658,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
@@ -2616,11 +2676,11 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-1900</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2634,8 +2694,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2726,8 +2789,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2818,8 +2884,11 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2839,11 +2908,11 @@
         <v>0</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>17700</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
@@ -2857,32 +2926,32 @@
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-300</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>800</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>100</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
@@ -2893,117 +2962,123 @@
         <v>0</v>
       </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-7500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-7200</v>
       </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
       <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3">
         <v>400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>43300</v>
+      </c>
+      <c r="E33" s="3">
         <v>44500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>68300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>91300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>58000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>32000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-63600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>75500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>60700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>82500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>68900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-14200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-17600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-92300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-38100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>28000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>9200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>29000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>64300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>10900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>4100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>26700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>65400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>12000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>5600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>35100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>48600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-4300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>20700</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3094,197 +3169,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>43300</v>
+      </c>
+      <c r="E35" s="3">
         <v>44500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>68300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>91300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>58000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>32000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-63600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>75500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>60700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>82500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>68900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-14200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-17600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-92300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-38100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>28000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>9200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>29000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>64300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>10900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>4100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>26700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>65400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>12000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>5600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>35100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>48600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-4300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>20700</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45193</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45102</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45011</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44920</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44829</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44738</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44647</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44556</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44465</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44374</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44283</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44192</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44101</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44010</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43919</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43828</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43737</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43464</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43282</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43191</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43002</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42911</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42820</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42729</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42638</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3317,8 +3401,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3351,100 +3436,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>111500</v>
+      </c>
+      <c r="E41" s="3">
         <v>86600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>88800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>94400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>84700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>90700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>95300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>97800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>87600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>76300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>101300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>136700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>110000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>160000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>181400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>403400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>67100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>51400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>64700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>82800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>71800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>78600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>81700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>105800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>128300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>98700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>103500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>98400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>127200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>91500</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3535,376 +3624,391 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>102800</v>
+      </c>
+      <c r="E43" s="3">
         <v>50800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>53500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>40000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>131900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>46400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>48800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>46000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>123100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>34500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>39700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>31300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>103500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>37400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>33900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>40100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>141100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>44900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>45700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>39700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>122300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>35100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>46200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>39300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>110700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>51900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>48900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>46900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>134900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>46300</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>75900</v>
+      </c>
+      <c r="E44" s="3">
         <v>70600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>62300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>67900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>78100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>83300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>80500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>68800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>79100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>72400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>59000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>53900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>61900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>58800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>63600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>68100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>86900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>73400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>69200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>73100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>72800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>48500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>48600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>50200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>51300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>51000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>52600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>52300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>65200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>66500</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>53000</v>
+      </c>
+      <c r="E45" s="3">
         <v>53200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>43300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>45500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>51800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>55400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>68300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>58700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>63000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>57400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>47100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>51100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>48500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>42000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>48700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>60900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>45400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>41900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>54300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>54200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>68600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>66200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>71600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>76000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>70000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>57100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>48200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>43800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>63200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>46000</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>343300</v>
+      </c>
+      <c r="E46" s="3">
         <v>261100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>247900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>247800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>346600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>275700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>292900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>271300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>352800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>240700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>247100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>273000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>323900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>298200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>327600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>572400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>340500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>211600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>233900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>249800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>335500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>228500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>248100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>271300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>360200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>258700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>253200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>241300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>390500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>250400</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3995,192 +4099,201 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2116900</v>
+      </c>
+      <c r="E48" s="3">
         <v>2130100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2065200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2028200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2017200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1990600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1974500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1965600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1972900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2004400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2016700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2028800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2060600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2092900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2142900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2245800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2302600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2312500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2334200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2355800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1115900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1129300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1141400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1167000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1173400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1184300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1194500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1195000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1237100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1418500</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>719300</v>
+      </c>
+      <c r="E49" s="3">
         <v>720200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>720300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>719200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>721400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>723100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>731400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>726500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>721900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>729500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>730100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>726500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>731100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>730800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>734400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>750700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>759100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>763100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>770800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>777500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>799400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>797700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>810100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>830000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>832500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>843000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>842600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>851800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>845600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>856800</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4271,8 +4384,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4363,100 +4479,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>244600</v>
+      </c>
+      <c r="E52" s="3">
         <v>239400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>239800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>236600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>235300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>229800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>231200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>239900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>246700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>244000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>252900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>257100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>246500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>245700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>228600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>197600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>190500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>181800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>172800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>169400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>214000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>195300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>190400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>186000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>195700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>187000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>190700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>222900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>169000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>134300</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4547,100 +4669,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3424100</v>
+      </c>
+      <c r="E54" s="3">
         <v>3350900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3273100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3231800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3320400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3219200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3230000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3203400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3294300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3218600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3246800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3285300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3362100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3367600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3433600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3766600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3592700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3468900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3511700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3552500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2464800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2350800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2389900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2454300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2561900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2473000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2480900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2511000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2642300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2660000</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4673,8 +4801,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4707,560 +4836,579 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>189200</v>
+      </c>
+      <c r="E57" s="3">
         <v>198100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>202200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>196100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>183700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>187800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>185600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>172700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>168000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>157400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>160100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>146800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>141500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>116300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>104800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>141200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>174900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>160000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>151500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>166300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>174500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>163700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>164800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>172300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>185500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>183400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>187800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>197600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>195400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>189700</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E58" s="3">
         <v>2400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1600</v>
-      </c>
-      <c r="H58" s="3">
-        <v>1500</v>
       </c>
       <c r="I58" s="3">
         <v>1500</v>
       </c>
       <c r="J58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K58" s="3">
         <v>11200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>11000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>11100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>11000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>41800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>38700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>35600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>32400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>29400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>26400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>26500</v>
-      </c>
-      <c r="U58" s="3">
-        <v>26700</v>
       </c>
       <c r="V58" s="3">
         <v>26700</v>
       </c>
       <c r="W58" s="3">
+        <v>26700</v>
+      </c>
+      <c r="X58" s="3">
         <v>27200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>26800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>26000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>25600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>26300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>58800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>44500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>48800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>35100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>39600</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>809900</v>
+      </c>
+      <c r="E59" s="3">
         <v>719300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>706900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>722100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>793500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>722000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>722700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>751700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>805700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>728700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>742300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>743300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>769900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>687100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>673700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>667400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>760700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>604200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>608400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>629000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>589400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>430100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>440400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>469500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>872400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>474500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>491900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>500400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>593000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>444800</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1002300</v>
+      </c>
+      <c r="E60" s="3">
         <v>919800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>911600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>920400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>978900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>911300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>909900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>935600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>984600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>897200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>913500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>932000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>950100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>839000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>810800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>838000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>962000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>790800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>786600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>822000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>791000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>620600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>631200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>667400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>813400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>716800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>724200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>746800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>823400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>674000</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>788100</v>
+      </c>
+      <c r="E61" s="3">
         <v>797100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>772000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>765700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>831700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>820200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>800200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>711000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>782100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>828100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>839000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>951500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>997800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1112300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1178400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1389300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1022300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1093400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1122200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1037600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1067600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1124000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1113800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1116600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1091800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1141900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1082000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>953600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1054400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1186100</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1221600</v>
+      </c>
+      <c r="E62" s="3">
         <v>1238100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1217600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1222800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1236000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1247500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1257200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1263400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1304700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1327000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1341300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1356400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1403300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1403800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1415100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1439200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1430900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1433200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1444400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1440600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>551300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>546000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>553500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>561900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>575500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>577100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>572900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>590900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>568600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>534300</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5351,8 +5499,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5443,8 +5594,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5535,100 +5689,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3015000</v>
+      </c>
+      <c r="E66" s="3">
         <v>2957800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2904200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2911800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3049100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2980700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2969200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2911800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3077800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3058800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3100500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3246700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3358000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3362500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3412500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3674700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3422300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3324700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3360900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3308400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2419000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2300400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2308600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2356600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2491600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2447300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2390700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2303800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2459600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2433300</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5661,8 +5821,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5753,8 +5914,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5845,8 +6009,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5937,8 +6104,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6029,100 +6199,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-528800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-554200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-582700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-635500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-706100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-735300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-733700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-634400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-698200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-758900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-762300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-844900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-918100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-903900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-886200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-794000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-755100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-783100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-792300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-714400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-920000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-915900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-902000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-898800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-913200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-961300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-891600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-781700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-786800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-747500</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6213,8 +6389,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6305,8 +6484,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6397,100 +6579,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>409100</v>
+      </c>
+      <c r="E76" s="3">
         <v>393100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>368900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>320000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>271400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>238500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>260800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>291600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>216500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>159800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>146300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>38600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>21100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>92000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>170300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>144300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>150800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>244200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>45700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>50400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>81200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>97700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>70300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>25700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>90200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>207100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>182700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>226800</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6581,197 +6769,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45193</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45102</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45011</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44920</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44829</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44738</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44647</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44556</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44465</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44374</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44283</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44192</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44101</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44010</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43919</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43828</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43737</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43464</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43282</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43191</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43002</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42911</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42820</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42729</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42638</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>43300</v>
+      </c>
+      <c r="E81" s="3">
         <v>44500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>68300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>91300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>58000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>32000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-63600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>75500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>60700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>82500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>68900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-14200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-17600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-92300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-38100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>28000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>9200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>29000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>64300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>10900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>4100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>26700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>65400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>12000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>5600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>35100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>48600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-4300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>20700</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6804,100 +7001,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>49300</v>
+      </c>
+      <c r="E83" s="3">
         <v>48000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>47600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>46300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>44400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>42200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>41300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>41800</v>
-      </c>
-      <c r="K83" s="3">
-        <v>40800</v>
       </c>
       <c r="L83" s="3">
         <v>40800</v>
       </c>
       <c r="M83" s="3">
+        <v>40800</v>
+      </c>
+      <c r="N83" s="3">
         <v>40500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>41200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>42800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>43400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>45800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>48300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>49600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>47900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>49800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>49500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>50100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>50600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>50800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>50100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>49800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>47800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>48100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>46600</v>
-      </c>
-      <c r="AE83" s="3">
-        <v>48600</v>
       </c>
       <c r="AF83" s="3">
         <v>48600</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>48600</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6988,8 +7189,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7080,8 +7284,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7172,8 +7379,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7264,8 +7474,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7356,100 +7569,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>158900</v>
+      </c>
+      <c r="E89" s="3">
         <v>86300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>97600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>189700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>98300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>73800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>71700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>147100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>98200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>21100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>142200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>141000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>83900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>58300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-31600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>28300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>136700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>48500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>48600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>83900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>132900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>55100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>48500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>51500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>186000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>39900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>46900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>136200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>117000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7482,100 +7701,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-97200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-84900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-77700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-64400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-82400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-60400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-36700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-40200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-37500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-33900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-34000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-17400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-20900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-13800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-19000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-34200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-44400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-36700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-36100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-44700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-61900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-53800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-44200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-48300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-76800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-67600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-58000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-116500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-150000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-261800</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7666,8 +7889,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7758,100 +7984,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-91600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-84900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-77700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-62900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-79700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-45700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-36600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-39200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-35700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-26500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-26000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-16600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-20500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-8200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-13200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-34800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-37600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-19900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-31800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-42000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-53000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-42400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-35700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-46200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-60600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-37900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-12200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-12400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>133100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>106000</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7884,35 +8116,36 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-20800</v>
+      </c>
+      <c r="E96" s="3">
         <v>-20900</v>
-      </c>
-      <c r="E96" s="3">
-        <v>-21000</v>
       </c>
       <c r="F96" s="3">
         <v>-21000</v>
       </c>
       <c r="G96" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="H96" s="3">
         <v>-12300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-12500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-12400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-12600</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
@@ -7932,52 +8165,55 @@
         <v>0</v>
       </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-17500</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-8700</v>
       </c>
       <c r="T96" s="3">
         <v>-8700</v>
       </c>
       <c r="U96" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="V96" s="3">
         <v>-9200</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-9100</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-8200</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-8300</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-8400</v>
       </c>
       <c r="Z96" s="3">
         <v>-8400</v>
       </c>
       <c r="AA96" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-7300</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-7400</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-8100</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-8300</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-7400</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-7800</v>
       </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8068,8 +8304,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8160,8 +8399,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8252,280 +8494,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-39600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-26200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-117000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-24700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-29800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-39800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-101100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-52200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-17200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-151100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-96900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-116600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-69800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-172700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>342300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-82900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-43000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-32000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-31400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-87400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-18700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-29200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-29100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-97300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-13000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-28900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-154400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-212200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-139100</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="E101" s="3">
         <v>700</v>
       </c>
       <c r="F101" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="G101" s="3">
         <v>0</v>
       </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>-2800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>2300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>2000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-3400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>1000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>1700</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-2300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>27800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-5600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>9700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-6100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>8800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>8500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-22500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-33600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>26300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-52100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-20000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-220900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>336300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>15700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-15400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-15900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>10900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-6800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-7600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-19600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-23700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>27100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-10100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>5100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-28800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>35700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-10600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BLMN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BLMN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
   <si>
     <t>BLMN</t>
   </si>
@@ -656,427 +656,440 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45193</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45102</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45011</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44920</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44829</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44738</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44647</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44556</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44465</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44374</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44283</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44192</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44101</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44010</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43919</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43828</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43737</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43464</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43282</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43191</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43002</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42911</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42820</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42729</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42638</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1195300</v>
+      </c>
+      <c r="E8" s="3">
         <v>1194200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1079800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1152700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1244700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1095000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1055800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1125200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1140500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1047100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1010500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1077400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>987500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>812500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>771300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>578500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1008300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1022200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>967100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1021900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1128100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1013100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>965000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1031800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1116500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1076400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>955600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1036500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1154700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1004100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1005400</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>357800</v>
+      </c>
+      <c r="E9" s="3">
         <v>352300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>321900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>351200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>384200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>326900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>332900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>364500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>359400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>321400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>304300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>311800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>291600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>247700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>230800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>179300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>313200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>312300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>300100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>312400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>351800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>313200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>307500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>322800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>352100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>332600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>296600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>323100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>364700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>310700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>322100</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>837500</v>
+      </c>
+      <c r="E10" s="3">
         <v>841900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>757900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>801500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>860500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>768100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>722900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>760700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>781100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>725700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>706200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>765600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>695900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>564800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>540500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>399200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>695100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>709900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>667000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>709500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>776300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>699900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>657500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>709000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>764400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>743800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>659000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>713400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>790000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>693400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>683300</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1110,8 +1123,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1205,8 +1219,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1300,103 +1317,109 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>146700</v>
+      </c>
+      <c r="E14" s="3">
         <v>34400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-6000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>3300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>107800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>4800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>63500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>7300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>2200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>16500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>42600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>71800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>2200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1400</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>2000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>2100</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-      <c r="AA14" s="3" t="s">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>800</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>300</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
       <c r="AF14" s="3">
         <v>0</v>
       </c>
       <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1404,94 +1427,97 @@
         <v>49300</v>
       </c>
       <c r="E15" s="3">
+        <v>49300</v>
+      </c>
+      <c r="F15" s="3">
         <v>48000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>47600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>46300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>44400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>42200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>41300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>41800</v>
-      </c>
-      <c r="L15" s="3">
-        <v>40800</v>
       </c>
       <c r="M15" s="3">
         <v>40800</v>
       </c>
       <c r="N15" s="3">
+        <v>40800</v>
+      </c>
+      <c r="O15" s="3">
         <v>40500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>41200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>42800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>43400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>45800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>48300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>49600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>47900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>49800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>49500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>50100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>50600</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>50800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>50100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>49800</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>47800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>48100</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>46600</v>
-      </c>
-      <c r="AF15" s="3">
-        <v>48600</v>
       </c>
       <c r="AG15" s="3">
         <v>48600</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>48600</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1522,198 +1548,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1254000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1137300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1021600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1063200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1124100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1010900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1004500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1145100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1033300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>968600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>995600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>954800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>896500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>819700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>785500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>690600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1049900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>979000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>945200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>978500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1045600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>991700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>952500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>998900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1038100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1061900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>950400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>995400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1077900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1008300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>974100</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-58700</v>
+      </c>
+      <c r="E18" s="3">
         <v>56900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>58200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>89500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>120600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>84100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>51300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-19900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>107200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>78500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>14900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>122600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>91000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-7200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-14200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-112100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-41600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>43200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>21900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>43400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>82500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>21400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>12500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>32900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>78400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>14500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>5200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>41100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>76800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-4200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>31300</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1747,8 +1780,9 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1771,11 +1805,11 @@
         <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-17700</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
@@ -1789,32 +1823,32 @@
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>300</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-800</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>-100</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
         <v>0</v>
       </c>
@@ -1825,405 +1859,420 @@
         <v>0</v>
       </c>
       <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>7500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>7200</v>
       </c>
-      <c r="AE20" s="3">
-        <v>0</v>
-      </c>
       <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>106200</v>
+        <v>-9400</v>
       </c>
       <c r="E21" s="3">
         <v>106200</v>
       </c>
       <c r="F21" s="3">
+        <v>106200</v>
+      </c>
+      <c r="G21" s="3">
         <v>137000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>166900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>128500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>93500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>149000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>119300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>55700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>163100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>132200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>35900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>29200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-65800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>5900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>92800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>69900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>93300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>131800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>71500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>63100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>83700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>128500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>64400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>60600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>96400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>123400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>44000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>81900</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E22" s="3">
         <v>13900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>12800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>13000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>12400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>14300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>12700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>12500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>13600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>13800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>14200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>15000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>14600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>17800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>18300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>16600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>11700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>12400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>13300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>12400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>11200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>11700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>11600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>11300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>10300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>12000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>10700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>9500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>9100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>12300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-72300</v>
+      </c>
+      <c r="E23" s="3">
         <v>42900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>45400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>76500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>108200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>69800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>38600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-50100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>93600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>64700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>107600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>76400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-24700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-32600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-128200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-54100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>30800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>8700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>31000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>71100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>9700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>21600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>68100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>38800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>67600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-16900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>23200</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-2600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>14800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>9700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>5600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>11500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>15900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-4500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>22700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>6600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-10500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-14800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-35800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-19700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>5500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-5100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-12100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>3000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>18000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-14200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2317,198 +2366,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-82300</v>
+      </c>
+      <c r="E26" s="3">
         <v>45600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>45400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>70000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>93400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>60100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>33100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-61700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>77700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>63200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>84900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>69800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-14200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-17800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-92400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-34400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>29300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>9400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>29800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>65600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>12400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>4300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>26700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>66100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>14700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>5300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>35800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>49600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-2700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>21200</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-83900</v>
+      </c>
+      <c r="E27" s="3">
         <v>43300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>44500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>68300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>91300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>58000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>32000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-63600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>75500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>60700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>82500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>68900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-14200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-17600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-92300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-38100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>28000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>9200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>29000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>64300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>10900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>4100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>26700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>65400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>13900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>5600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>35100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>48600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-4300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>20700</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2602,8 +2660,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2661,8 +2722,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
@@ -2679,11 +2740,11 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-1900</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2697,8 +2758,11 @@
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2792,8 +2856,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2887,8 +2954,11 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2911,11 +2981,11 @@
         <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>17700</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
@@ -2929,32 +2999,32 @@
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-300</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>800</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>100</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
         <v>0</v>
       </c>
@@ -2965,120 +3035,126 @@
         <v>0</v>
       </c>
       <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-7500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-7200</v>
       </c>
-      <c r="AE32" s="3">
-        <v>0</v>
-      </c>
       <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
         <v>400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-83900</v>
+      </c>
+      <c r="E33" s="3">
         <v>43300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>44500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>68300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>91300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>58000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>32000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-63600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>75500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>60700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>82500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>68900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-14200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-17600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-92300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-38100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>28000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>9200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>29000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>64300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>10900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>4100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>26700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>65400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>12000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>5600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>35100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>48600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-4300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>20700</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3172,203 +3248,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-83900</v>
+      </c>
+      <c r="E35" s="3">
         <v>43300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>44500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>68300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>91300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>58000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>32000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-63600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>75500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>60700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>82500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>68900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-14200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-17600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-92300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-38100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>28000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>9200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>29000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>64300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>10900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>4100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>26700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>65400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>12000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>5600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>35100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>48600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-4300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>20700</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45193</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45102</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45011</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44920</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44829</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44738</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44647</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44556</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44465</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44374</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44283</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44192</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44101</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44010</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43919</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43828</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43737</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43464</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43282</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43191</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43002</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42911</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42820</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42729</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42638</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3402,8 +3487,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3437,103 +3523,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>131700</v>
+      </c>
+      <c r="E41" s="3">
         <v>111500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>86600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>88800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>94400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>84700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>90700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>95300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>97800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>87600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>76300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>101300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>136700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>110000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>160000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>181400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>403400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>67100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>51400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>64700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>82800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>71800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>78600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>81700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>105800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>128300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>98700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>103500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>98400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>127200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>91500</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3627,388 +3717,403 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>50900</v>
+      </c>
+      <c r="E43" s="3">
         <v>102800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>50800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>53500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>40000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>131900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>46400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>48800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>46000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>123100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>34500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>39700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>31300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>103500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>37400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>33900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>40100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>141100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>44900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>45700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>39700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>122300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>35100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>46200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>39300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>110700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>51900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>48900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>46900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>134900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>46300</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>65200</v>
+      </c>
+      <c r="E44" s="3">
         <v>75900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>70600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>62300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>67900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>78100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>83300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>80500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>68800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>79100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>72400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>59000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>53900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>61900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>58800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>63600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>68100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>86900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>73400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>69200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>73100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>72800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>48500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>48600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>50200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>51300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>51000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>52600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>52300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>65200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>66500</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>50400</v>
+      </c>
+      <c r="E45" s="3">
         <v>53000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>53200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>43300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>45500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>51800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>55400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>68300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>58700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>63000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>57400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>47100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>51100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>48500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>42000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>48700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>60900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>45400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>41900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>54300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>54200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>68600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>66200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>71600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>76000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>70000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>57100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>48200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>43800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>63200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>46000</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>298200</v>
+      </c>
+      <c r="E46" s="3">
         <v>343300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>261100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>247900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>247800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>346600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>275700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>292900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>271300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>352800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>240700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>247100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>273000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>323900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>298200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>327600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>572400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>340500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>211600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>233900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>249800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>335500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>228500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>248100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>271300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>360200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>258700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>253200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>241300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>390500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>250400</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4102,198 +4207,207 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2132900</v>
+      </c>
+      <c r="E48" s="3">
         <v>2116900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2130100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2065200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2028200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2017200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1990600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1974500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1965600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1972900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2004400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2016700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2028800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2060600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2092900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2142900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2245800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2302600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2312500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2334200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2355800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1115900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1129300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1141400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1167000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1173400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1184300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1194500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1195000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1237100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1418500</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>717100</v>
+      </c>
+      <c r="E49" s="3">
         <v>719300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>720200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>720300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>719200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>721400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>723100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>731400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>726500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>721900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>729500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>730100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>726500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>731100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>730800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>734400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>750700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>759100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>763100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>770800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>777500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>799400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>797700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>810100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>830000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>832500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>843000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>842600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>851800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>845600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>856800</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4387,8 +4501,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4482,103 +4599,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>246000</v>
+      </c>
+      <c r="E52" s="3">
         <v>244600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>239400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>239800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>236600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>235300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>229800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>231200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>239900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>246700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>244000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>252900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>257100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>246500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>245700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>228600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>197600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>190500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>181800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>172800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>169400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>214000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>195300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>190400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>186000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>195700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>187000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>190700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>222900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>169000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>134300</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4672,103 +4795,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3394200</v>
+      </c>
+      <c r="E54" s="3">
         <v>3424100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3350900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3273100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3231800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3320400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3219200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3230000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3203400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3294300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3218600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3246800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3285300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3362100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3367600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3433600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3766600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3592700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3468900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3511700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>3552500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2464800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2350800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2389900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2454300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2561900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2473000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2480900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2511000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2642300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>2660000</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4802,8 +4931,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4837,578 +4967,597 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>177700</v>
+      </c>
+      <c r="E57" s="3">
         <v>189200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>198100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>202200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>196100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>183700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>187800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>185600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>172700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>168000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>157400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>160100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>146800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>141500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>116300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>104800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>141200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>174900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>160000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>151500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>166300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>174500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>163700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>164800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>172300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>185500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>183400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>187800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>197600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>195400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>189700</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E58" s="3">
         <v>3200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1600</v>
-      </c>
-      <c r="I58" s="3">
-        <v>1500</v>
       </c>
       <c r="J58" s="3">
         <v>1500</v>
       </c>
       <c r="K58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L58" s="3">
         <v>11200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>11000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>11100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>11000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>41800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>38700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>35600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>32400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>29400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>26400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>26500</v>
-      </c>
-      <c r="V58" s="3">
-        <v>26700</v>
       </c>
       <c r="W58" s="3">
         <v>26700</v>
       </c>
       <c r="X58" s="3">
+        <v>26700</v>
+      </c>
+      <c r="Y58" s="3">
         <v>27200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>26800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>26000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>25600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>26300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>58800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>44500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>48800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>35100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>39600</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>713500</v>
+      </c>
+      <c r="E59" s="3">
         <v>809900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>719300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>706900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>722100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>793500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>722000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>722700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>751700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>805700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>728700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>742300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>743300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>769900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>687100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>673700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>667400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>760700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>604200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>608400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>629000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>589400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>430100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>440400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>469500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>872400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>474500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>491900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>500400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>593000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>444800</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>894100</v>
+      </c>
+      <c r="E60" s="3">
         <v>1002300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>919800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>911600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>920400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>978900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>911300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>909900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>935600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>984600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>897200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>913500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>932000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>950100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>839000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>810800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>838000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>962000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>790800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>786600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>822000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>791000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>620600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>631200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>667400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>813400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>716800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>724200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>746800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>823400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>674000</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>958900</v>
+      </c>
+      <c r="E61" s="3">
         <v>788100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>797100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>772000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>765700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>831700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>820200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>800200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>711000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>782100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>828100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>839000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>951500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>997800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1112300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1178400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1389300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1022300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1093400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1122200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1037600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1067600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1124000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1113800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1116600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1091800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1141900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1082000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>953600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1054400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1186100</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1235900</v>
+      </c>
+      <c r="E62" s="3">
         <v>1221600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1238100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1217600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1222800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1236000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1247500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1257200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1263400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1304700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1327000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1341300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1356400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1403300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1403800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1415100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1439200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1430900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1433200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1444400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1440600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>551300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>546000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>553500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>561900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>575500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>577100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>572900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>590900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>568600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>534300</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5502,8 +5651,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5597,8 +5749,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5692,103 +5847,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3091600</v>
+      </c>
+      <c r="E66" s="3">
         <v>3015000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2957800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2904200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2911800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3049100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2980700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2969200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2911800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3077800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3058800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3100500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3246700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3358000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3362500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3412500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3674700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3422300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3324700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3360900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3308400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2419000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2300400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2308600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2356600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2491600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2447300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2390700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2303800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2459600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2433300</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5822,8 +5983,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5917,8 +6079,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6012,8 +6177,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6107,8 +6275,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6202,103 +6373,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-809900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-528800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-554200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-582700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-635500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-706100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-735300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-733700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-634400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-698200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-758900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-762300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-844900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-918100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-903900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-886200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-794000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-755100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-783100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-792300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-714400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-920000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-915900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-902000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-898800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-913200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-961300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-891600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-781700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-786800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-747500</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6392,8 +6569,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6487,8 +6667,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6582,103 +6765,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>302700</v>
+      </c>
+      <c r="E76" s="3">
         <v>409100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>393100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>368900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>320000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>271400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>238500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>260800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>291600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>216500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>159800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>146300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>38600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>5100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>21100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>92000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>170300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>144300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>150800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>244200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>45700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>50400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>81200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>97700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>70300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>25700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>90200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>207100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>182700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>226800</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6772,203 +6961,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45193</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45102</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45011</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44920</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44829</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44738</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44647</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44556</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44465</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44374</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44283</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44192</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44101</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44010</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43919</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43828</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43737</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43464</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43282</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43191</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43002</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42911</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42820</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42729</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42638</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-83900</v>
+      </c>
+      <c r="E81" s="3">
         <v>43300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>44500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>68300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>91300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>58000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>32000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-63600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>75500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>60700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>82500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>68900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-14200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-17600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-92300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-38100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>28000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>9200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>29000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>64300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>10900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>4100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>26700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>65400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>12000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>5600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>35100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>48600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-4300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>20700</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7002,8 +7200,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7011,94 +7210,97 @@
         <v>49300</v>
       </c>
       <c r="E83" s="3">
+        <v>49300</v>
+      </c>
+      <c r="F83" s="3">
         <v>48000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>47600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>46300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>44400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>42200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>41300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>41800</v>
-      </c>
-      <c r="L83" s="3">
-        <v>40800</v>
       </c>
       <c r="M83" s="3">
         <v>40800</v>
       </c>
       <c r="N83" s="3">
+        <v>40800</v>
+      </c>
+      <c r="O83" s="3">
         <v>40500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>41200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>42800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>43400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>45800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>48300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>49600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>47900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>49800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>49500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>50100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>50600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>50800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>50100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>49800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>47800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>48100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>46600</v>
-      </c>
-      <c r="AF83" s="3">
-        <v>48600</v>
       </c>
       <c r="AG83" s="3">
         <v>48600</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>48600</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7192,8 +7394,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7287,8 +7492,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7382,8 +7590,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7477,8 +7688,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7572,103 +7786,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>73800</v>
+      </c>
+      <c r="E89" s="3">
         <v>158900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>86300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>97600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>189700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>98300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>73800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>71700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>147100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>98200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>21100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>142200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>141000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>83900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>58300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-31600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>28300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>136700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>48500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>48600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>83900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>132900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>55100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>48500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>51500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>186000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>39900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>46900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>136200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>117000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7702,103 +7922,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-64900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-97200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-84900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-77700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-64400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-82400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-60400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-36700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-40200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-37500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-33900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-34000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-17400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-20900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-13800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-19000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-34200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-44400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-36700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-36100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-44700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-61900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-53800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-44200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-48300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-76800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-67600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-58000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-116500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-150000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-261800</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7892,8 +8116,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7987,103 +8214,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-64600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-91600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-84900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-77700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-62900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-79700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-45700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-36600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-39200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-35700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-26500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-26000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-16600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-20500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-8200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-13200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-34800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-37600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-19900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-31800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-42000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-53000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-42400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-35700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-46200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-60600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-37900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-12200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-12400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>133100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>106000</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8117,38 +8350,39 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-21100</v>
+      </c>
+      <c r="E96" s="3">
         <v>-20800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-20900</v>
-      </c>
-      <c r="F96" s="3">
-        <v>-21000</v>
       </c>
       <c r="G96" s="3">
         <v>-21000</v>
       </c>
       <c r="H96" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="I96" s="3">
         <v>-12300</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-12500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-12400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-12600</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -8168,52 +8402,55 @@
         <v>0</v>
       </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-17500</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-8700</v>
       </c>
       <c r="U96" s="3">
         <v>-8700</v>
       </c>
       <c r="V96" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="W96" s="3">
         <v>-9200</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-9100</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-8200</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-8300</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-8400</v>
       </c>
       <c r="AA96" s="3">
         <v>-8400</v>
       </c>
       <c r="AB96" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-7300</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-7400</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-8100</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-8300</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-7400</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-7800</v>
       </c>
     </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8307,8 +8544,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8402,8 +8642,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8497,289 +8740,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-39600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-26200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-117000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-24700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-29800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-39800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-101100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-52200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-17200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-151100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-96900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-116600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-69800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-172700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>342300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-82900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-43000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-32000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-31400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-87400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-18700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-29200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-29100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-97300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-13000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-28900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-154400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-212200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-139100</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E101" s="3">
         <v>100</v>
-      </c>
-      <c r="E101" s="3">
-        <v>700</v>
       </c>
       <c r="F101" s="3">
         <v>700</v>
       </c>
       <c r="G101" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="H101" s="3">
         <v>0</v>
       </c>
       <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>-2800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>2300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>2000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-3400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>1000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-700</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>1700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-2300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E102" s="3">
         <v>27800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-5600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>9700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-6100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>8800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>8500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-22500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-33600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>26300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-52100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-20000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-220900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>336300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>15700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-15400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-15900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>10900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-6800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-7600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-19600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-23700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>27100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-10100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>5100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-28800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>35700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-10600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BLMN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BLMN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
   <si>
     <t>BLMN</t>
   </si>
@@ -656,440 +656,453 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45193</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45102</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45011</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44920</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44829</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44738</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44647</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44556</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44465</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44374</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44283</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44192</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44101</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44010</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43919</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43828</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43737</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43464</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43282</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43191</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43002</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42911</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42820</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42729</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42638</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1118900</v>
+      </c>
+      <c r="E8" s="3">
         <v>1195300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1194200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1079800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1152700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1244700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1095000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1055800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1125200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1140500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1047100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1010500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1077400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>987500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>812500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>771300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>578500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1008300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1022200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>967100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1021900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1128100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1013100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>965000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1031800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1116500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1076400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>955600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1036500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1154700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1004100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1005400</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>336100</v>
+      </c>
+      <c r="E9" s="3">
         <v>357800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>352300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>321900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>351200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>384200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>326900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>332900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>364500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>359400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>321400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>304300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>311800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>291600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>247700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>230800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>179300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>313200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>312300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>300100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>312400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>351800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>313200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>307500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>322800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>352100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>332600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>296600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>323100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>364700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>310700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>322100</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>782800</v>
+      </c>
+      <c r="E10" s="3">
         <v>837500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>841900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>757900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>801500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>860500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>768100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>722900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>760700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>781100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>725700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>706200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>765600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>695900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>564800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>540500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>399200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>695100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>709900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>667000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>709500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>776300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>699900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>657500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>709000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>764400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>743800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>659000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>713400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>790000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>693400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>683300</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1124,8 +1137,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1222,8 +1236,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1320,204 +1337,213 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E14" s="3">
         <v>146700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>34400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-6000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>3300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>107800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>4800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>63500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>7300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>16500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>42600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>71800</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>2200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1400</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>2000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>2100</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
         <v>0</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-      <c r="AB14" s="3" t="s">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>800</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>300</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
       <c r="AG14" s="3">
         <v>0</v>
       </c>
       <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>49300</v>
+        <v>49500</v>
       </c>
       <c r="E15" s="3">
         <v>49300</v>
       </c>
       <c r="F15" s="3">
+        <v>49300</v>
+      </c>
+      <c r="G15" s="3">
         <v>48000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>47600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>46300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>44400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>42200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>41300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>41800</v>
-      </c>
-      <c r="M15" s="3">
-        <v>40800</v>
       </c>
       <c r="N15" s="3">
         <v>40800</v>
       </c>
       <c r="O15" s="3">
+        <v>40800</v>
+      </c>
+      <c r="P15" s="3">
         <v>40500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>41200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>42800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>43400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>45800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>48300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>49600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>47900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>49800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>49500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>50100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>50600</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>50800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>50100</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>49800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>47800</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>48100</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>46600</v>
-      </c>
-      <c r="AG15" s="3">
-        <v>48600</v>
       </c>
       <c r="AH15" s="3">
         <v>48600</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>48600</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1549,204 +1575,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1072700</v>
+      </c>
+      <c r="E17" s="3">
         <v>1254000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1137300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1021600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1063200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1124100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1010900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1004500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1145100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1033300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>968600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>995600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>954800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>896500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>819700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>785500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>690600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1049900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>979000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>945200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>978500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1045600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>991700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>952500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>998900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1038100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1061900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>950400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>995400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1077900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1008300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>974100</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>46200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-58700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>56900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>58200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>89500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>120600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>84100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>51300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-19900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>107200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>78500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>14900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>122600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>91000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-7200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-14200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-112100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-41600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>43200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>21900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>43400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>82500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>21400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>12500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>32900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>78400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>14500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>5200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>41100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>76800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-4200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>31300</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1781,8 +1814,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1808,11 +1842,11 @@
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-17700</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
@@ -1826,32 +1860,32 @@
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>300</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-800</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-100</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
         <v>0</v>
       </c>
@@ -1862,417 +1896,432 @@
         <v>0</v>
       </c>
       <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3">
         <v>100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>7500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>7200</v>
       </c>
-      <c r="AF20" s="3">
-        <v>0</v>
-      </c>
       <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>95700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-9400</v>
-      </c>
-      <c r="E21" s="3">
-        <v>106200</v>
       </c>
       <c r="F21" s="3">
         <v>106200</v>
       </c>
       <c r="G21" s="3">
+        <v>106200</v>
+      </c>
+      <c r="H21" s="3">
         <v>137000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>166900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>128500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>93500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>149000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>119300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>55700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>163100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>132200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>35900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>29200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-65800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>5900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>92800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>69900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>93300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>131800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>71500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>63100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>83700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>128500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>64400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>60600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>96400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>123400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>44000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>81900</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E22" s="3">
         <v>13600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>13900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>12800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>13000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>12400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>14300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>12700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>12500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>13600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>13800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>14200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>15000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>14600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>17800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>18300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>16600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>11700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>12400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>13300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>12400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>11200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>11700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>11600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>11300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>10300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>12000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>10700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>9500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>9100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>12300</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>31300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-72300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>42900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>45400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>76500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>108200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>69800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>38600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-50100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>93600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>64700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>107600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>76400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-24700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-32600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-128200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-54100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>30800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>8700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>31000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>71100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>9700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>21600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>68100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>38800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>67600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-16900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>23200</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E24" s="3">
         <v>10000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-2600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>14800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>9700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>11500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>15900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-4500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>22700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>6600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-10500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-14800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-35800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-19700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>5500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-3300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-5100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-12100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-3200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>3000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>18000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-14200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2369,204 +2418,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>29600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-82300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>45600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>45400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>70000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>93400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>60100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>33100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-61700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>77700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>63200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>84900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>69800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-14200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-17800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-92400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-34400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>29300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>9400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>29800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>65600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>12400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>4300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>26700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>66100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>14700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>5300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>35800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>49600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-2700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>21200</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>28400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-83900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>43300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>44500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>68300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>91300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>58000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>32000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-63600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>75500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>60700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>82500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>68900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-14200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-17600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-92300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-38100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>28000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>9200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>29000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>64300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>10900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>4100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>26700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>65400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>13900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>5600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>35100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>48600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-4300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>20700</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2663,8 +2721,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2725,8 +2786,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
@@ -2743,11 +2804,11 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-1900</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2761,8 +2822,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2859,8 +2923,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2957,8 +3024,11 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2984,11 +3054,11 @@
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>17700</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
@@ -3002,32 +3072,32 @@
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-300</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>800</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>100</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
         <v>0</v>
       </c>
@@ -3038,123 +3108,129 @@
         <v>0</v>
       </c>
       <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-7500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-7200</v>
       </c>
-      <c r="AF32" s="3">
-        <v>0</v>
-      </c>
       <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
         <v>400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>28400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-83900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>43300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>44500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>68300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>91300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>58000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>32000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-63600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>75500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>60700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>82500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>68900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-14200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-17600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-92300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-38100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>28000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>9200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>29000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>64300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>10900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>4100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>26700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>65400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>12000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>5600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>35100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>48600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-4300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>20700</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3251,209 +3327,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>28400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-83900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>43300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>44500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>68300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>91300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>58000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>32000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-63600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>75500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>60700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>82500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>68900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-14200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-17600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-92300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-38100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>28000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>9200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>29000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>64300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>10900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>4100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>26700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>65400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>12000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>5600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>35100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>48600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-4300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>20700</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45193</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45102</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45011</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44920</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44829</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44738</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44647</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44556</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44465</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44374</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44283</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44192</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44101</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44010</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43919</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43828</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43737</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43464</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43282</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43191</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43002</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42911</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42820</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42729</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42638</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3488,8 +3573,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3524,106 +3610,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>117900</v>
+      </c>
+      <c r="E41" s="3">
         <v>131700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>111500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>86600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>88800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>94400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>84700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>90700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>95300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>97800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>87600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>76300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>101300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>136700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>110000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>160000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>181400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>403400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>67100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>51400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>64700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>82800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>71800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>78600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>81700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>105800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>128300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>98700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>103500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>98400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>127200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>91500</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3720,400 +3810,415 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>55800</v>
+      </c>
+      <c r="E43" s="3">
         <v>50900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>102800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>50800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>53500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>40000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>131900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>46400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>48800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>46000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>123100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>34500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>39700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>31300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>103500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>37400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>33900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>40100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>141100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>44900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>45700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>39700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>122300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>35100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>46200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>39300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>110700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>51900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>48900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>46900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>134900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>46300</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>74100</v>
+      </c>
+      <c r="E44" s="3">
         <v>65200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>75900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>70600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>62300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>67900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>78100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>83300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>80500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>68800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>79100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>72400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>59000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>53900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>61900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>58800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>63600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>68100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>86900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>73400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>69200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>73100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>72800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>48500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>48600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>50200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>51300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>51000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>52600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>52300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>65200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>66500</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>52400</v>
+      </c>
+      <c r="E45" s="3">
         <v>50400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>53000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>53200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>43300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>45500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>51800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>55400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>68300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>58700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>63000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>57400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>47100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>51100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>48500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>42000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>48700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>60900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>45400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>41900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>54300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>54200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>68600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>66200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>71600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>76000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>70000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>57100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>48200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>43800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>63200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>46000</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>300200</v>
+      </c>
+      <c r="E46" s="3">
         <v>298200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>343300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>261100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>247900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>247800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>346600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>275700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>292900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>271300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>352800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>240700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>247100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>273000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>323900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>298200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>327600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>572400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>340500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>211600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>233900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>249800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>335500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>228500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>248100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>271300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>360200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>258700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>253200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>241300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>390500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>250400</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4210,204 +4315,213 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2130700</v>
+      </c>
+      <c r="E48" s="3">
         <v>2132900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2116900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2130100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2065200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2028200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2017200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1990600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1974500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1965600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1972900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2004400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2016700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2028800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2060600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2092900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2142900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2245800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2302600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2312500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2334200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2355800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1115900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1129300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1141400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1167000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1173400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1184300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1194500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1195000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1237100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1418500</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>711900</v>
+      </c>
+      <c r="E49" s="3">
         <v>717100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>719300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>720200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>720300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>719200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>721400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>723100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>731400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>726500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>721900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>729500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>730100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>726500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>731100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>730800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>734400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>750700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>759100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>763100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>770800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>777500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>799400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>797700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>810100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>830000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>832500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>843000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>842600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>851800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>845600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>856800</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4504,8 +4618,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4602,106 +4719,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>251300</v>
+      </c>
+      <c r="E52" s="3">
         <v>246000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>244600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>239400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>239800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>236600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>235300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>229800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>231200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>239900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>246700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>244000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>252900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>257100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>246500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>245700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>228600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>197600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>190500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>181800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>172800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>169400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>214000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>195300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>190400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>186000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>195700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>187000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>190700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>222900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>169000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>134300</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4798,8 +4921,11 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -4807,97 +4933,100 @@
         <v>3394200</v>
       </c>
       <c r="E54" s="3">
+        <v>3394200</v>
+      </c>
+      <c r="F54" s="3">
         <v>3424100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3350900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3273100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3231800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3320400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3219200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3230000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3203400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3294300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3218600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3246800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3285300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3362100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3367600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3433600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3766600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3592700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3468900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>3511700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>3552500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2464800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2350800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2389900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2454300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2561900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2473000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2480900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2511000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>2642300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>2660000</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4932,8 +5061,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4968,596 +5098,615 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>178200</v>
+      </c>
+      <c r="E57" s="3">
         <v>177700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>189200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>198100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>202200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>196100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>183700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>187800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>185600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>172700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>168000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>157400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>160100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>146800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>141500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>116300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>104800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>141200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>174900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>160000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>151500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>166300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>174500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>163700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>164800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>172300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>185500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>183400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>187800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>197600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>195400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>189700</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E58" s="3">
         <v>2800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1600</v>
-      </c>
-      <c r="J58" s="3">
-        <v>1500</v>
       </c>
       <c r="K58" s="3">
         <v>1500</v>
       </c>
       <c r="L58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="M58" s="3">
         <v>11200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>11000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>11100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>11000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>41800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>38700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>35600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>32400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>29400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>26400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>26500</v>
-      </c>
-      <c r="W58" s="3">
-        <v>26700</v>
       </c>
       <c r="X58" s="3">
         <v>26700</v>
       </c>
       <c r="Y58" s="3">
+        <v>26700</v>
+      </c>
+      <c r="Z58" s="3">
         <v>27200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>26800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>26000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>25600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>26300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>58800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>44500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>48800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>35100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>39600</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>686600</v>
+      </c>
+      <c r="E59" s="3">
         <v>713500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>809900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>719300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>706900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>722100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>793500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>722000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>722700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>751700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>805700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>728700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>742300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>743300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>769900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>687100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>673700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>667400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>760700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>604200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>608400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>629000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>589400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>430100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>440400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>469500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>872400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>474500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>491900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>500400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>593000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>444800</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>867300</v>
+      </c>
+      <c r="E60" s="3">
         <v>894100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1002300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>919800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>911600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>920400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>978900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>911300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>909900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>935600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>984600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>897200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>913500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>932000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>950100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>839000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>810800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>838000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>962000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>790800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>786600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>822000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>791000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>620600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>631200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>667400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>813400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>716800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>724200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>746800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>823400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>674000</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1008700</v>
+      </c>
+      <c r="E61" s="3">
         <v>958900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>788100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>797100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>772000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>765700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>831700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>820200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>800200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>711000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>782100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>828100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>839000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>951500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>997800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1112300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1178400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1389300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1022300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1093400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1122200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1037600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1067600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1124000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1113800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1116600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1091800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1141900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1082000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>953600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1054400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1186100</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1228500</v>
+      </c>
+      <c r="E62" s="3">
         <v>1235900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1221600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1238100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1217600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1222800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1236000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1247500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1257200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1263400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1304700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1327000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1341300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1356400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1403300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1403800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1415100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1439200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1430900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1433200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1444400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1440600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>551300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>546000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>553500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>561900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>575500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>577100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>572900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>590900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>568600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>534300</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5654,8 +5803,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5752,8 +5904,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5850,106 +6005,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3107400</v>
+      </c>
+      <c r="E66" s="3">
         <v>3091600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3015000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2957800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2904200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2911800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3049100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2980700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2969200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2911800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3077800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3058800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3100500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3246700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3358000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3362500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3412500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3674700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3422300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3324700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3360900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3308400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2419000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2300400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2308600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2356600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2491600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2447300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2390700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2303800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2459600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2433300</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5984,8 +6145,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6082,8 +6244,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6180,8 +6345,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6278,8 +6446,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6376,106 +6547,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-834900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-809900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-528800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-554200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-582700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-635500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-706100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-735300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-733700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-634400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-698200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-758900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-762300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-844900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-918100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-903900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-886200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-794000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-755100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-783100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-792300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-714400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-920000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-915900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-902000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-898800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-913200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-961300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-891600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-781700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-786800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-747500</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6572,8 +6749,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6670,8 +6850,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6768,106 +6951,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>286800</v>
+      </c>
+      <c r="E76" s="3">
         <v>302700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>409100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>393100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>368900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>320000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>271400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>238500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>260800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>291600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>216500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>159800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>146300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>38600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>5100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>21100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>92000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>170300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>144300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>150800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>244200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>45700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>50400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>81200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>97700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>70300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>25700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>90200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>207100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>182700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>226800</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6964,209 +7153,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45193</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45102</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45011</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44920</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44829</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44738</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44647</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44556</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44465</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44374</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44283</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44192</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44101</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44010</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43919</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43828</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43737</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43464</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43282</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43191</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43002</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42911</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42820</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42729</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42638</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>28400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-83900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>43300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>44500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>68300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>91300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>58000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>32000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-63600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>75500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>60700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>82500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>68900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-14200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-17600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-92300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-38100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>28000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>9200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>29000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>64300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>10900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>4100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>26700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>65400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>12000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>5600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>35100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>48600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-4300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>20700</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7201,106 +7399,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>49300</v>
+        <v>49500</v>
       </c>
       <c r="E83" s="3">
         <v>49300</v>
       </c>
       <c r="F83" s="3">
+        <v>49300</v>
+      </c>
+      <c r="G83" s="3">
         <v>48000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>47600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>46300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>44400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>42200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>41300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>41800</v>
-      </c>
-      <c r="M83" s="3">
-        <v>40800</v>
       </c>
       <c r="N83" s="3">
         <v>40800</v>
       </c>
       <c r="O83" s="3">
+        <v>40800</v>
+      </c>
+      <c r="P83" s="3">
         <v>40500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>41200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>42800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>43400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>45800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>48300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>49600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>47900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>49800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>49500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>50100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>50600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>50800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>50100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>49800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>47800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>48100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>46600</v>
-      </c>
-      <c r="AG83" s="3">
-        <v>48600</v>
       </c>
       <c r="AH83" s="3">
         <v>48600</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>48600</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7397,8 +7599,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7495,8 +7700,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7593,8 +7801,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7691,8 +7902,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7789,106 +8003,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>42400</v>
+      </c>
+      <c r="E89" s="3">
         <v>73800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>158900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>86300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>97600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>189700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>98300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>73800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>71700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>147100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>98200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>21100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>142200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>141000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>83900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>58300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-31600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>28300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>136700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>48500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>48600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>83900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>132900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>55100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>48500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>51500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>186000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>39900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>46900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>136200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>117000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7923,106 +8143,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-66600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-64900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-97200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-84900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-77700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-64400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-82400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-60400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-36700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-40200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-37500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-33900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-34000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-17400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-20900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-13800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-19000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-34200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-44400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-36700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-36100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-44700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-61900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-53800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-44200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-48300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-76800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-67600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-58000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-116500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-150000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-261800</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8119,8 +8343,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8217,106 +8444,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-66600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-64600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-91600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-84900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-77700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-62900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-79700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-45700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-36600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-39200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-35700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-26500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-26000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-16600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-20500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-8200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-13200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-34800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-37600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-19900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-31800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-42000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-53000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-42400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-35700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-46200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-60600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-37900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-12200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-12400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>133100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>106000</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8351,41 +8584,42 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-20800</v>
+      </c>
+      <c r="E96" s="3">
         <v>-21100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-20800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-20900</v>
-      </c>
-      <c r="G96" s="3">
-        <v>-21000</v>
       </c>
       <c r="H96" s="3">
         <v>-21000</v>
       </c>
       <c r="I96" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="J96" s="3">
         <v>-12300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-12500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-12400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-12600</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
@@ -8405,52 +8639,55 @@
         <v>0</v>
       </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-17500</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-8700</v>
       </c>
       <c r="V96" s="3">
         <v>-8700</v>
       </c>
       <c r="W96" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="X96" s="3">
         <v>-9200</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-9100</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-8200</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-8300</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-8400</v>
       </c>
       <c r="AB96" s="3">
         <v>-8400</v>
       </c>
       <c r="AC96" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-7300</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-7400</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-8100</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-8300</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-7400</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-7800</v>
       </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8547,8 +8784,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8645,8 +8885,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8743,298 +8986,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E100" s="3">
         <v>8800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-39600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-26200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-117000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-24700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-29800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-39800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-101100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-52200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-17200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-151100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-96900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-116600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-69800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-172700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>342300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-82900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-43000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-32000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-31400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-87400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-18700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-29200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-29100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-97300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-13000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-28900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-154400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-212200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-139100</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>100</v>
-      </c>
-      <c r="F101" s="3">
-        <v>700</v>
       </c>
       <c r="G101" s="3">
         <v>700</v>
       </c>
       <c r="H101" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="I101" s="3">
         <v>0</v>
       </c>
       <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
         <v>-2800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>2300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>2000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-3400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-1000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>1000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>1700</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-2300</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="E102" s="3">
         <v>17300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>27800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-5600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>9700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-6100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-4600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>8800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>8500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-22500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-33600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>26300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-52100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-20000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-220900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>336300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>15700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-15400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-15900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>10900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-6800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-7600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-19600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-23700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>27100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-10100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>5100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-28800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>35700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-10600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BLMN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BLMN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
   <si>
     <t>BLMN</t>
   </si>
@@ -656,453 +656,466 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45193</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45102</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45011</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44920</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44829</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44738</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44647</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44556</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44465</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44374</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44283</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44192</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44101</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44010</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43919</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43828</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43737</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43464</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43282</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43191</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43002</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42911</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42820</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42729</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42638</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1038800</v>
+      </c>
+      <c r="E8" s="3">
         <v>1118900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1195300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1194200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1079800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1152700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1244700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1095000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1055800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1125200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1140500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1047100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1010500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1077400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>987500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>812500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>771300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>578500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1008300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1022200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>967100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1021900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1128100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1013100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>965000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1031800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1116500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1076400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>955600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1036500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1154700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1004100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1005400</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>336100</v>
+        <v>897300</v>
       </c>
       <c r="E9" s="3">
-        <v>357800</v>
+        <v>945800</v>
       </c>
       <c r="F9" s="3">
-        <v>352300</v>
+        <v>991300</v>
       </c>
       <c r="G9" s="3">
-        <v>321900</v>
+        <v>984700</v>
       </c>
       <c r="H9" s="3">
-        <v>351200</v>
+        <v>917400</v>
       </c>
       <c r="I9" s="3">
-        <v>384200</v>
+        <v>950500</v>
       </c>
       <c r="J9" s="3">
+        <v>1008700</v>
+      </c>
+      <c r="K9" s="3">
         <v>326900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>332900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>364500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>359400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>321400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>304300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>311800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>291600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>247700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>230800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>179300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>313200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>312300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>300100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>312400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>351800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>313200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>307500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>322800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>352100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>332600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>296600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>323100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>364700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>310700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>322100</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>782800</v>
+        <v>141500</v>
       </c>
       <c r="E10" s="3">
-        <v>837500</v>
+        <v>173100</v>
       </c>
       <c r="F10" s="3">
-        <v>841900</v>
+        <v>204000</v>
       </c>
       <c r="G10" s="3">
-        <v>757900</v>
+        <v>209400</v>
       </c>
       <c r="H10" s="3">
-        <v>801500</v>
+        <v>162500</v>
       </c>
       <c r="I10" s="3">
-        <v>860500</v>
+        <v>202200</v>
       </c>
       <c r="J10" s="3">
+        <v>236100</v>
+      </c>
+      <c r="K10" s="3">
         <v>768100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>722900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>760700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>781100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>725700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>706200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>765600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>695900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>564800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>540500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>399200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>695100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>709900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>667000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>709500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>776300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>699900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>657500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>709000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>764400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>743800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>659000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>713400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>790000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>693400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>683300</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1138,8 +1151,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1152,8 +1166,8 @@
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>8</v>
+      <c r="G12" s="3">
+        <v>3500</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>8</v>
@@ -1239,8 +1253,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1340,210 +1357,219 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E14" s="3">
         <v>16300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>146700</v>
       </c>
-      <c r="F14" s="3">
-        <v>34400</v>
-      </c>
       <c r="G14" s="3">
+        <v>34900</v>
+      </c>
+      <c r="H14" s="3">
         <v>-6000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>3300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>107800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>4800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>63500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>7300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>2200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>16500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>42600</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>71800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>2200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>1400</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>2000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>2100</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
         <v>0</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-      <c r="AC14" s="3" t="s">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>800</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>300</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
       <c r="AH14" s="3">
         <v>0</v>
       </c>
       <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>50200</v>
+      </c>
+      <c r="E15" s="3">
         <v>49500</v>
-      </c>
-      <c r="E15" s="3">
-        <v>49300</v>
       </c>
       <c r="F15" s="3">
         <v>49300</v>
       </c>
       <c r="G15" s="3">
+        <v>49300</v>
+      </c>
+      <c r="H15" s="3">
         <v>48000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>47600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>46300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>44400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>42200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>41300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>41800</v>
-      </c>
-      <c r="N15" s="3">
-        <v>40800</v>
       </c>
       <c r="O15" s="3">
         <v>40800</v>
       </c>
       <c r="P15" s="3">
+        <v>40800</v>
+      </c>
+      <c r="Q15" s="3">
         <v>40500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>41200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>42800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>43400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>45800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>48300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>49600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>47900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>49800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>49500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>50100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>50600</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>50800</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>50100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>49800</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>47800</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>48100</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>46600</v>
-      </c>
-      <c r="AH15" s="3">
-        <v>48600</v>
       </c>
       <c r="AI15" s="3">
         <v>48600</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>48600</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1576,210 +1602,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1072700</v>
+        <v>1020300</v>
       </c>
       <c r="E17" s="3">
-        <v>1254000</v>
+        <v>1056500</v>
       </c>
       <c r="F17" s="3">
-        <v>1137300</v>
+        <v>1107400</v>
       </c>
       <c r="G17" s="3">
-        <v>1021600</v>
+        <v>1102500</v>
       </c>
       <c r="H17" s="3">
-        <v>1063200</v>
+        <v>1027600</v>
       </c>
       <c r="I17" s="3">
-        <v>1124100</v>
+        <v>1061400</v>
       </c>
       <c r="J17" s="3">
+        <v>1120800</v>
+      </c>
+      <c r="K17" s="3">
         <v>1010900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1004500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1145100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1033300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>968600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>995600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>954800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>896500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>819700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>785500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>690600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1049900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>979000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>945200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>978500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1045600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>991700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>952500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>998900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1038100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1061900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>950400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>995400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1077900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1008300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>974100</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>46200</v>
+        <v>18500</v>
       </c>
       <c r="E18" s="3">
-        <v>-58700</v>
+        <v>62400</v>
       </c>
       <c r="F18" s="3">
-        <v>56900</v>
+        <v>88000</v>
       </c>
       <c r="G18" s="3">
-        <v>58200</v>
+        <v>91700</v>
       </c>
       <c r="H18" s="3">
-        <v>89500</v>
+        <v>52200</v>
       </c>
       <c r="I18" s="3">
-        <v>120600</v>
+        <v>91300</v>
       </c>
       <c r="J18" s="3">
+        <v>124000</v>
+      </c>
+      <c r="K18" s="3">
         <v>84100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>51300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-19900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>107200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>78500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>14900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>122600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>91000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-7200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-14200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-112100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-41600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>43200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>21900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>43400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>82500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>21400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>12500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>32900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>78400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>14500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>5200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>41100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>76800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-4200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>31300</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1815,41 +1848,42 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-17700</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
@@ -1863,32 +1897,32 @@
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>300</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-800</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-100</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
         <v>0</v>
       </c>
@@ -1899,429 +1933,444 @@
         <v>0</v>
       </c>
       <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
         <v>100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>7500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>7200</v>
       </c>
-      <c r="AG20" s="3">
-        <v>0</v>
-      </c>
       <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="3">
         <v>-400</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>95700</v>
+        <v>68700</v>
       </c>
       <c r="E21" s="3">
-        <v>-9400</v>
+        <v>111900</v>
       </c>
       <c r="F21" s="3">
-        <v>106200</v>
+        <v>137200</v>
       </c>
       <c r="G21" s="3">
-        <v>106200</v>
+        <v>141000</v>
       </c>
       <c r="H21" s="3">
-        <v>137000</v>
+        <v>100200</v>
       </c>
       <c r="I21" s="3">
-        <v>166900</v>
+        <v>138800</v>
       </c>
       <c r="J21" s="3">
+        <v>170300</v>
+      </c>
+      <c r="K21" s="3">
         <v>128500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>93500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>149000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>119300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>55700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>163100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>132200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>35900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>29200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-65800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>5900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>92800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>69900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>93300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>131800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>71500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>63100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>83700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>128500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>64400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>60600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>96400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>123400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>44000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>81900</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E22" s="3">
         <v>14800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>13600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>13900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>12800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>13000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>12400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>14300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>12700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>12500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>13600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>13800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>14200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>15000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>14600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>17800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>18300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>16600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>11700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>12400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>13300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>12400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>11200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>11700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>11600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>11300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>10300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>12000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>10700</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>9500</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>9100</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>12300</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E23" s="3">
         <v>31300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-72300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>42900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>45400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>76500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>108200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>69800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>38600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-50100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>93600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>64700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>107600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>76400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-24700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-32600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-128200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-54100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>30800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>8700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>31000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>71100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>9700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>21600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>68100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>38800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>67600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-16900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>23200</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="E24" s="3">
         <v>1700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>10000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-2600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>14800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>9700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>11500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>15900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-4500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>22700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>6600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-10500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-14800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-35800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-19700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>5500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-2700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-5100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-12100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-3200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>3000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>18000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-14200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2421,210 +2470,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E26" s="3">
         <v>29600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-82300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>45600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>45400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>70000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>93400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>60100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>33100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-61700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>77700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>63200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>84900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>69800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-14200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-17800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-92400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-34400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>29300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>9400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>29800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>65600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>12400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>4300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>26700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>66100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>14700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>5300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>35800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>49600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-2700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>21200</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E27" s="3">
         <v>28400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-83900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>43300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>44500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>68300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>91300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>58000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>32000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-63600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>75500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>60700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>82500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>68900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-14200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-17600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-92300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-38100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>28000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>9200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>29000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>64300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>10900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>4100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>26700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>65400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>13900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>5600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>35100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>48600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-4300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>20700</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2724,8 +2782,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2789,8 +2850,8 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
@@ -2807,11 +2868,11 @@
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-1900</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -2825,8 +2886,11 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2926,8 +2990,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3027,41 +3094,44 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>17700</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
@@ -3075,32 +3145,32 @@
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-300</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>800</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>100</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
         <v>0</v>
       </c>
@@ -3111,126 +3181,132 @@
         <v>0</v>
       </c>
       <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-7500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-7200</v>
       </c>
-      <c r="AG32" s="3">
-        <v>0</v>
-      </c>
       <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3">
         <v>400</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E33" s="3">
         <v>28400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-83900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>43300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>44500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>68300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>91300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>58000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>32000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-63600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>75500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>60700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>3400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>82500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>68900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-14200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-17600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-92300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-38100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>28000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>9200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>29000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>64300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>10900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>4100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>26700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>65400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>12000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>5600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>35100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>48600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-4300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>20700</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3330,215 +3406,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E35" s="3">
         <v>28400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-83900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>43300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>44500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>68300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>91300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>58000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>32000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-63600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>75500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>60700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>3400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>82500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>68900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-14200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-17600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-92300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-38100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>28000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>9200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>29000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>64300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>10900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>4100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>26700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>65400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>12000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>5600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>35100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>48600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-4300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>20700</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45193</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45102</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45011</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44920</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44829</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44738</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44647</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44556</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44465</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44374</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44283</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44192</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44101</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44010</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43919</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43828</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43737</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43464</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43282</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43191</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43002</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42911</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42820</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42729</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42638</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3574,8 +3659,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3611,109 +3697,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>83600</v>
+      </c>
+      <c r="E41" s="3">
         <v>117900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>131700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>111500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>86600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>88800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>94400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>84700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>90700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>95300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>97800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>87600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>76300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>101300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>136700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>110000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>160000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>181400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>403400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>67100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>51400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>64700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>82800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>71800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>78600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>81700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>105800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>128300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>98700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>103500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>98400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>127200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>91500</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3813,435 +3903,450 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>56700</v>
+      </c>
+      <c r="E43" s="3">
         <v>55800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>50900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>102800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>50800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>53500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>40000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>131900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>46400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>48800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>46000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>123100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>34500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>39700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>31300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>103500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>37400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>33900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>40100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>141100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>44900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>45700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>39700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>122300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>35100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>46200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>39300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>110700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>51900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>48900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>46900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>134900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>46300</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>71900</v>
+      </c>
+      <c r="E44" s="3">
         <v>74100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>65200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>75900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>70600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>62300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>67900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>78100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>83300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>80500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>68800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>79100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>72400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>59000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>53900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>61900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>58800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>63600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>68100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>86900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>73400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>69200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>73100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>72800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>48500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>48600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>50200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>51300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>51000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>52600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>52300</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>65200</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>66500</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>52400</v>
+        <v>18700</v>
       </c>
       <c r="E45" s="3">
-        <v>50400</v>
+        <v>20200</v>
       </c>
       <c r="F45" s="3">
-        <v>53000</v>
+        <v>19800</v>
       </c>
       <c r="G45" s="3">
-        <v>53200</v>
+        <v>23500</v>
       </c>
       <c r="H45" s="3">
-        <v>43300</v>
+        <v>21500</v>
       </c>
       <c r="I45" s="3">
-        <v>45500</v>
+        <v>18900</v>
       </c>
       <c r="J45" s="3">
+        <v>17700</v>
+      </c>
+      <c r="K45" s="3">
         <v>51800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>55400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>68300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>58700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>63000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>57400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>47100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>51100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>48500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>42000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>48700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>60900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>45400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>41900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>54300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>54200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>68600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>66200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>71600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>76000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>70000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>57100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>48200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>43800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>63200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>46000</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>261100</v>
+      </c>
+      <c r="E46" s="3">
         <v>300200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>298200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>343300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>261100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>247900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>247800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>346600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>275700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>292900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>271300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>352800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>240700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>247100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>273000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>323900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>298200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>327600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>572400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>340500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>211600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>233900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>249800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>335500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>228500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>248100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>271300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>360200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>258700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>253200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>241300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>390500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>250400</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4318,210 +4423,219 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2150900</v>
+      </c>
+      <c r="E48" s="3">
         <v>2130700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2132900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2116900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2130100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2065200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2028200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2017200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1990600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1974500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1965600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1972900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2004400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2016700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2028800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2060600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2092900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2142900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2245800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2302600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2312500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2334200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2355800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1115900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1129300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1141400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1167000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1173400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1184300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1194500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1195000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1237100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1418500</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>728800</v>
+      </c>
+      <c r="E49" s="3">
         <v>711900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>717100</v>
       </c>
-      <c r="F49" s="3">
-        <v>719300</v>
-      </c>
       <c r="G49" s="3">
+        <v>742400</v>
+      </c>
+      <c r="H49" s="3">
         <v>720200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>720300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>719200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>721400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>723100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>731400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>726500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>721900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>729500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>730100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>726500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>731100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>730800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>734400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>750700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>759100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>763100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>770800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>777500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>799400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>797700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>810100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>830000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>832500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>843000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>842600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>851800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>845600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>856800</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4621,8 +4735,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4722,109 +4839,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>251300</v>
+        <v>103700</v>
       </c>
       <c r="E52" s="3">
-        <v>246000</v>
+        <v>86400</v>
       </c>
       <c r="F52" s="3">
-        <v>244600</v>
+        <v>87900</v>
       </c>
       <c r="G52" s="3">
-        <v>239400</v>
+        <v>58200</v>
       </c>
       <c r="H52" s="3">
-        <v>239800</v>
+        <v>84600</v>
       </c>
       <c r="I52" s="3">
-        <v>236600</v>
+        <v>87400</v>
       </c>
       <c r="J52" s="3">
+        <v>85100</v>
+      </c>
+      <c r="K52" s="3">
         <v>235300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>229800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>231200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>239900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>246700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>244000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>252900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>257100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>246500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>245700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>228600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>197600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>190500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>181800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>172800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>169400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>214000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>195300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>190400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>186000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>195700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>187000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>190700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>222900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>169000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>134300</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4924,109 +5047,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>3394200</v>
+        <v>3433600</v>
       </c>
       <c r="E54" s="3">
         <v>3394200</v>
       </c>
       <c r="F54" s="3">
+        <v>3394200</v>
+      </c>
+      <c r="G54" s="3">
         <v>3424100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3350900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3273100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3231800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3320400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3219200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3230000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3203400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3294300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3218600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3246800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3285300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3362100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3367600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3433600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3766600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3592700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>3468900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>3511700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>3552500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2464800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2350800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2389900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2454300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2561900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2473000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2480900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>2511000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>2642300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>2660000</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5062,8 +5191,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5099,614 +5229,633 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>168300</v>
+      </c>
+      <c r="E57" s="3">
         <v>178200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>177700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>189200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>198100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>202200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>196100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>183700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>187800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>185600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>172700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>168000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>157400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>160100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>146800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>141500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>116300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>104800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>141200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>174900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>160000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>151500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>166300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>174500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>163700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>164800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>172300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>185500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>183400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>187800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>197600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>195400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>189700</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2400</v>
+        <v>171900</v>
       </c>
       <c r="E58" s="3">
-        <v>2800</v>
+        <v>171800</v>
       </c>
       <c r="F58" s="3">
-        <v>3200</v>
+        <v>174000</v>
       </c>
       <c r="G58" s="3">
-        <v>2400</v>
+        <v>178600</v>
       </c>
       <c r="H58" s="3">
-        <v>2500</v>
+        <v>188000</v>
       </c>
       <c r="I58" s="3">
-        <v>2300</v>
+        <v>187900</v>
       </c>
       <c r="J58" s="3">
+        <v>185000</v>
+      </c>
+      <c r="K58" s="3">
         <v>1600</v>
-      </c>
-      <c r="K58" s="3">
-        <v>1500</v>
       </c>
       <c r="L58" s="3">
         <v>1500</v>
       </c>
       <c r="M58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="N58" s="3">
         <v>11200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>11000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>11100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>11000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>41800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>38700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>35600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>32400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>29400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>26400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>26500</v>
-      </c>
-      <c r="X58" s="3">
-        <v>26700</v>
       </c>
       <c r="Y58" s="3">
         <v>26700</v>
       </c>
       <c r="Z58" s="3">
+        <v>26700</v>
+      </c>
+      <c r="AA58" s="3">
         <v>27200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>26800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>26000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>25600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>26300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>58800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>44500</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>48800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>35100</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>39600</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>686600</v>
+        <v>418800</v>
       </c>
       <c r="E59" s="3">
-        <v>713500</v>
+        <v>421100</v>
       </c>
       <c r="F59" s="3">
-        <v>809900</v>
+        <v>446700</v>
       </c>
       <c r="G59" s="3">
-        <v>719300</v>
+        <v>516300</v>
       </c>
       <c r="H59" s="3">
-        <v>706900</v>
+        <v>313000</v>
       </c>
       <c r="I59" s="3">
-        <v>722100</v>
+        <v>329000</v>
       </c>
       <c r="J59" s="3">
+        <v>338500</v>
+      </c>
+      <c r="K59" s="3">
         <v>793500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>722000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>722700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>751700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>805700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>728700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>742300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>743300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>769900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>687100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>673700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>667400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>760700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>604200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>608400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>629000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>589400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>430100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>440400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>469500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>872400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>474500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>491900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>500400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>593000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>444800</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>849000</v>
+      </c>
+      <c r="E60" s="3">
         <v>867300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>894100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1002300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>919800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>911600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>920400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>978900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>911300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>909900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>935600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>984600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>897200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>913500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>932000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>950100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>839000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>810800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>838000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>962000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>790800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>786600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>822000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>791000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>620600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>631200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>667400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>813400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>716800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>724200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>746800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>823400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>674000</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1008700</v>
+        <v>2243100</v>
       </c>
       <c r="E61" s="3">
-        <v>958900</v>
+        <v>2143600</v>
       </c>
       <c r="F61" s="3">
-        <v>788100</v>
+        <v>2098300</v>
       </c>
       <c r="G61" s="3">
-        <v>797100</v>
+        <v>1919800</v>
       </c>
       <c r="H61" s="3">
-        <v>772000</v>
+        <v>1948800</v>
       </c>
       <c r="I61" s="3">
-        <v>765700</v>
+        <v>1904100</v>
       </c>
       <c r="J61" s="3">
+        <v>1902400</v>
+      </c>
+      <c r="K61" s="3">
         <v>831700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>820200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>800200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>711000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>782100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>828100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>839000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>951500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>997800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1112300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1178400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1389300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1022300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1093400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1122200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1037600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1067600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1124000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1113800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1116600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1091800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1141900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1082000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>953600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1054400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1186100</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1228500</v>
+        <v>92600</v>
       </c>
       <c r="E62" s="3">
-        <v>1235900</v>
+        <v>89700</v>
       </c>
       <c r="F62" s="3">
-        <v>1221600</v>
+        <v>92400</v>
       </c>
       <c r="G62" s="3">
-        <v>1238100</v>
+        <v>90000</v>
       </c>
       <c r="H62" s="3">
-        <v>1217600</v>
+        <v>82300</v>
       </c>
       <c r="I62" s="3">
-        <v>1222800</v>
+        <v>81500</v>
       </c>
       <c r="J62" s="3">
+        <v>81900</v>
+      </c>
+      <c r="K62" s="3">
         <v>1236000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1247500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1257200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1263400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1304700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1327000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1341300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1356400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1403300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1403800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1415100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1439200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1430900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1433200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1444400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1440600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>551300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>546000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>553500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>561900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>575500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>577100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>572900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>590900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>568600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>534300</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5806,8 +5955,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5907,8 +6059,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6008,109 +6163,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>3107400</v>
+        <v>3188600</v>
       </c>
       <c r="E66" s="3">
-        <v>3091600</v>
+        <v>3104500</v>
       </c>
       <c r="F66" s="3">
-        <v>3015000</v>
+        <v>3088800</v>
       </c>
       <c r="G66" s="3">
-        <v>2957800</v>
+        <v>3012100</v>
       </c>
       <c r="H66" s="3">
-        <v>2904200</v>
+        <v>2955000</v>
       </c>
       <c r="I66" s="3">
+        <v>2901300</v>
+      </c>
+      <c r="J66" s="3">
+        <v>2909000</v>
+      </c>
+      <c r="K66" s="3">
+        <v>3049100</v>
+      </c>
+      <c r="L66" s="3">
+        <v>2980700</v>
+      </c>
+      <c r="M66" s="3">
+        <v>2969200</v>
+      </c>
+      <c r="N66" s="3">
         <v>2911800</v>
       </c>
-      <c r="J66" s="3">
-        <v>3049100</v>
-      </c>
-      <c r="K66" s="3">
-        <v>2980700</v>
-      </c>
-      <c r="L66" s="3">
-        <v>2969200</v>
-      </c>
-      <c r="M66" s="3">
-        <v>2911800</v>
-      </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3077800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3058800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3100500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3246700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3358000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3362500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3412500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3674700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3422300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3324700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3360900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3308400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2419000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2300400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2308600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2356600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2491600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2447300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2390700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2303800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2459600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>2433300</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6146,8 +6307,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6247,8 +6409,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6348,8 +6513,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6449,8 +6617,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6550,109 +6721,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-846400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-834900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-809900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-528800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-554200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-582700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-635500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-706100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-735300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-733700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-634400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-698200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-758900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-762300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-844900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-918100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-903900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-886200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-794000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-755100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-783100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-792300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-714400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-920000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-915900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-902000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-898800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-913200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-961300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-891600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-781700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-786800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-747500</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6752,8 +6929,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6853,8 +7033,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6954,109 +7137,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>242100</v>
+      </c>
+      <c r="E76" s="3">
         <v>286800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>302700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>409100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>393100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>368900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>320000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>271400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>238500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>260800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>291600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>216500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>159800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>146300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>38600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>5100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>21100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>92000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>170300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>144300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>150800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>244200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>45700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>50400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>81200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>97700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>70300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>25700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>90200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>207100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>182700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>226800</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7156,215 +7345,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45193</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45102</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45011</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44920</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44829</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44738</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44647</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44556</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44465</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44374</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44283</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44192</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44101</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44010</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43919</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43828</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43737</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43464</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43282</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43191</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43002</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42911</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42820</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42729</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42638</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E81" s="3">
         <v>28400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-83900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>43300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>44500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>68300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>91300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>58000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>32000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-63600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>75500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>60700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>3400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>82500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>68900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-14200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-17600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-92300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-38100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>28000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>9200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>29000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>64300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>10900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>4100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>26700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>65400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>12000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>5600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>35100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>48600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-4300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>20700</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7400,109 +7598,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>49500</v>
+        <v>48000</v>
       </c>
       <c r="E83" s="3">
-        <v>49300</v>
+        <v>47600</v>
       </c>
       <c r="F83" s="3">
-        <v>49300</v>
+        <v>46300</v>
       </c>
       <c r="G83" s="3">
-        <v>48000</v>
+        <v>38200</v>
       </c>
       <c r="H83" s="3">
-        <v>47600</v>
+        <v>42200</v>
       </c>
       <c r="I83" s="3">
-        <v>46300</v>
+        <v>41300</v>
       </c>
       <c r="J83" s="3">
+        <v>41800</v>
+      </c>
+      <c r="K83" s="3">
         <v>44400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>42200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>41300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>41800</v>
-      </c>
-      <c r="N83" s="3">
-        <v>40800</v>
       </c>
       <c r="O83" s="3">
         <v>40800</v>
       </c>
       <c r="P83" s="3">
+        <v>40800</v>
+      </c>
+      <c r="Q83" s="3">
         <v>40500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>41200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>42800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>43400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>45800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>48300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>49600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>47900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>49800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>49500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>50100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>50600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>50800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>50100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>49800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>47800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>48100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>46600</v>
-      </c>
-      <c r="AH83" s="3">
-        <v>48600</v>
       </c>
       <c r="AI83" s="3">
         <v>48600</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>48600</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7602,8 +7804,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7703,8 +7908,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7804,8 +8012,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7905,8 +8116,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8006,109 +8220,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="E89" s="3">
         <v>42400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>73800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>158900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>86300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>97600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>189700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>98300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>73800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>71700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>147100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>98200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>21100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>142200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>141000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>83900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>58300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-31600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>28300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>136700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>48500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>48600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>83900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>132900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>55100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>48500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>51500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>186000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>39900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>46900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>136200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>117000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8144,109 +8364,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-67200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-66600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-64900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-97200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-84900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-77700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-64400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-82400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-60400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-36700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-40200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-37500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-33900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-34000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-17400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-20900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-13800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-19000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-34200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-44400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-36700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-36100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-44700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-61900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-53800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-44200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-48300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-76800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-67600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-58000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-116500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-150000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-261800</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8346,8 +8570,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8447,109 +8674,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-65300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-66600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-64600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-91600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-84900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-77700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-62900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-79700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-45700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-36600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-39200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-35700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-26500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-26000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-16600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-20500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-8200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-13200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-34800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-37600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-19900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-31800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-42000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-53000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-42400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-35700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-46200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-60600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-37900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-12200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-12400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>133100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>106000</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8585,44 +8818,45 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-20800</v>
+        <v>20400</v>
       </c>
       <c r="E96" s="3">
-        <v>-21100</v>
+        <v>20800</v>
       </c>
       <c r="F96" s="3">
-        <v>-20800</v>
+        <v>21100</v>
       </c>
       <c r="G96" s="3">
-        <v>-20900</v>
+        <v>20800</v>
       </c>
       <c r="H96" s="3">
-        <v>-21000</v>
+        <v>20900</v>
       </c>
       <c r="I96" s="3">
-        <v>-21000</v>
+        <v>21000</v>
       </c>
       <c r="J96" s="3">
+        <v>21000</v>
+      </c>
+      <c r="K96" s="3">
         <v>-12300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-12500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-12400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-12600</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
@@ -8642,52 +8876,55 @@
         <v>0</v>
       </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-17500</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-8700</v>
       </c>
       <c r="W96" s="3">
         <v>-8700</v>
       </c>
       <c r="X96" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-9200</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-9100</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-8200</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-8300</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-8400</v>
       </c>
       <c r="AC96" s="3">
         <v>-8400</v>
       </c>
       <c r="AD96" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-7300</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-7400</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-8100</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-8300</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-7400</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-7800</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8787,8 +9024,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8888,8 +9128,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8989,307 +9232,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>43300</v>
+      </c>
+      <c r="E100" s="3">
         <v>13500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>8800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-39600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-26200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-117000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-24700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-29800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-39800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-101100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-52200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-17200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-151100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-96900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-116600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-69800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-172700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>342300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-82900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-43000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-32000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-31400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-87400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-18700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-29200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-29100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-97300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-13000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-28900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-154400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-212200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-139100</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-3000</v>
+        <v>700</v>
       </c>
       <c r="E101" s="3">
+        <v>700</v>
+      </c>
+      <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="I101" s="3">
+        <v>2300</v>
+      </c>
+      <c r="J101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="M101" s="3">
+        <v>2300</v>
+      </c>
+      <c r="N101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="O101" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="P101" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>1400</v>
+      </c>
+      <c r="R101" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="S101" s="3">
+        <v>1100</v>
+      </c>
+      <c r="T101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="U101" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="V101" s="3">
+        <v>400</v>
+      </c>
+      <c r="W101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="X101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>500</v>
+      </c>
+      <c r="AA101" s="3">
+        <v>700</v>
+      </c>
+      <c r="AB101" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="AC101" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="AD101" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AF101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AG101" s="3">
         <v>-700</v>
       </c>
-      <c r="F101" s="3">
-        <v>100</v>
-      </c>
-      <c r="G101" s="3">
-        <v>700</v>
-      </c>
-      <c r="H101" s="3">
-        <v>700</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="L101" s="3">
-        <v>2300</v>
-      </c>
-      <c r="M101" s="3">
-        <v>2000</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="O101" s="3">
-        <v>100</v>
-      </c>
-      <c r="P101" s="3">
-        <v>1400</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="R101" s="3">
-        <v>1100</v>
-      </c>
-      <c r="S101" s="3">
-        <v>-300</v>
-      </c>
-      <c r="T101" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="U101" s="3">
-        <v>400</v>
-      </c>
-      <c r="V101" s="3">
-        <v>-400</v>
-      </c>
-      <c r="W101" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="X101" s="3">
-        <v>-600</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>500</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>700</v>
-      </c>
-      <c r="AA101" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="AB101" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="AC101" s="3">
-        <v>100</v>
-      </c>
-      <c r="AD101" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="AE101" s="3">
-        <v>1000</v>
-      </c>
-      <c r="AF101" s="3">
-        <v>-700</v>
-      </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>1700</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-2300</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-34300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-13700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>17300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>27800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-5600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>9700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-6100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-4600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>8800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>8500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-22500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-33600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>26300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-52100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-20000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-220900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>336300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>15700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-15400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-15900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>10900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-6800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-7600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-19600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-23700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>27100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-10100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>5100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-28800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>35700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-10600</v>
       </c>
     </row>
